--- a/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 2.xlsx
+++ b/exercise/Admin/Admin Ekspedisi/Tes Excel Admin Ekspedisi 2.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Ekspedisi 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Ekspedisi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C31F9A-8984-4706-A5F4-A61E6C5BFF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7908EC30-5FA3-4D9B-92C1-FF38C18F5D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -440,12 +451,15 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -454,9 +468,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -483,9 +494,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -523,9 +534,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -558,26 +569,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -610,26 +604,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -812,7 +789,7 @@
     <col min="1" max="1" width="0.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
@@ -824,14 +801,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="21" t="s">
+      <c r="D1" s="16"/>
+      <c r="E1" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="21"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="2:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
@@ -872,16 +849,37 @@
       <c r="C3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="11" t="str">
+        <f>VLOOKUP(VALUE(LEFT(C3,1)),$C$19:$E$23,2,FALSE)</f>
+        <v>Pelabuhan 1</v>
+      </c>
       <c r="E3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="14"/>
+      <c r="F3" s="11" t="str">
+        <f>VLOOKUP(VALUE(LEFT(C3,1)),$C$19:$E$23,3,FALSE)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="G3" s="11" t="str">
+        <f>INDEX($H$20:$K$20,MATCH(RIGHT(C3,3),$H$19:$K$19))</f>
+        <v>Surabaya</v>
+      </c>
+      <c r="H3" s="11" t="str">
+        <f>INDEX($H$21:$K$21,MATCH(RIGHT(C3,3),$H$19:$K$19))</f>
+        <v>Singapura</v>
+      </c>
+      <c r="I3" s="11" t="str">
+        <f>INDEX($D$27:$D$30,MATCH(G3,$C$27:$C$30,0))</f>
+        <v>Mobil</v>
+      </c>
+      <c r="J3" s="11" t="str">
+        <f>INDEX($G$27:$G$30,MATCH(H3,$F$27:$F$30,0))</f>
+        <v>Semen</v>
+      </c>
+      <c r="K3" s="14">
+        <f>VLOOKUP(D3,$I$26:$K$30,2,FALSE)+VLOOKUP(D3,$I$26:$K$30,3,FALSE)</f>
+        <v>675000</v>
+      </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
@@ -890,16 +888,37 @@
       <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="11" t="str">
+        <f t="shared" ref="D4:D12" si="0">VLOOKUP(VALUE(LEFT(C4,1)),$C$19:$E$23,2,FALSE)</f>
+        <v>Pelabuhan 2</v>
+      </c>
       <c r="E4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="14"/>
+      <c r="F4" s="11" t="str">
+        <f t="shared" ref="F4:F12" si="1">VLOOKUP(VALUE(LEFT(C4,1)),$C$19:$E$23,3,FALSE)</f>
+        <v>William</v>
+      </c>
+      <c r="G4" s="11" t="str">
+        <f t="shared" ref="G4:G12" si="2">INDEX($H$20:$K$20,MATCH(RIGHT(C4,3),$H$19:$K$19))</f>
+        <v>Belawan</v>
+      </c>
+      <c r="H4" s="11" t="str">
+        <f t="shared" ref="H4:H12" si="3">INDEX($H$21:$K$21,MATCH(RIGHT(C4,3),$H$19:$K$19))</f>
+        <v>Pekan Baru</v>
+      </c>
+      <c r="I4" s="11" t="str">
+        <f t="shared" ref="I4:I12" si="4">INDEX($D$27:$D$30,MATCH(G4,$C$27:$C$30,0))</f>
+        <v>Gyosun</v>
+      </c>
+      <c r="J4" s="11" t="str">
+        <f t="shared" ref="J4:J12" si="5">INDEX($G$27:$G$30,MATCH(H4,$F$27:$F$30,0))</f>
+        <v>Kertas</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" ref="K4:K12" si="6">VLOOKUP(D4,$I$26:$K$30,2,FALSE)+VLOOKUP(D4,$I$26:$K$30,3,FALSE)</f>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
@@ -908,16 +927,37 @@
       <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 4</v>
+      </c>
       <c r="E5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="14"/>
+      <c r="F5" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Michael</v>
+      </c>
+      <c r="G5" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Medan</v>
+      </c>
+      <c r="H5" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Padang</v>
+      </c>
+      <c r="I5" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Pasir Kwarsa</v>
+      </c>
+      <c r="J5" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Pupuk</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="6"/>
+        <v>1250000</v>
+      </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -926,16 +966,37 @@
       <c r="C6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 1</v>
+      </c>
       <c r="E6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="14"/>
+      <c r="F6" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Kevin</v>
+      </c>
+      <c r="G6" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Surabaya</v>
+      </c>
+      <c r="H6" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Singapura</v>
+      </c>
+      <c r="I6" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Mobil</v>
+      </c>
+      <c r="J6" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Semen</v>
+      </c>
+      <c r="K6" s="14">
+        <f t="shared" si="6"/>
+        <v>675000</v>
+      </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -944,16 +1005,37 @@
       <c r="C7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 1</v>
+      </c>
       <c r="E7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="14"/>
+      <c r="F7" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Kevin</v>
+      </c>
+      <c r="G7" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Jakarta</v>
+      </c>
+      <c r="H7" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Surabaya</v>
+      </c>
+      <c r="I7" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>CPO</v>
+      </c>
+      <c r="J7" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Kaca Besi</v>
+      </c>
+      <c r="K7" s="14">
+        <f t="shared" si="6"/>
+        <v>675000</v>
+      </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -962,16 +1044,37 @@
       <c r="C8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 2</v>
+      </c>
       <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="14"/>
+      <c r="F8" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>William</v>
+      </c>
+      <c r="G8" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Jakarta</v>
+      </c>
+      <c r="H8" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Surabaya</v>
+      </c>
+      <c r="I8" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>CPO</v>
+      </c>
+      <c r="J8" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Kaca Besi</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="6"/>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -980,16 +1083,37 @@
       <c r="C9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 3</v>
+      </c>
       <c r="E9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="14"/>
+      <c r="F9" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Daniel</v>
+      </c>
+      <c r="G9" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Belawan</v>
+      </c>
+      <c r="H9" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Pekan Baru</v>
+      </c>
+      <c r="I9" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Gyosun</v>
+      </c>
+      <c r="J9" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Kertas</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="6"/>
+        <v>900000</v>
+      </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -998,16 +1122,37 @@
       <c r="C10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 2</v>
+      </c>
       <c r="E10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="14"/>
+      <c r="F10" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>William</v>
+      </c>
+      <c r="G10" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Belawan</v>
+      </c>
+      <c r="H10" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Pekan Baru</v>
+      </c>
+      <c r="I10" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Gyosun</v>
+      </c>
+      <c r="J10" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Kertas</v>
+      </c>
+      <c r="K10" s="14">
+        <f t="shared" si="6"/>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -1016,16 +1161,37 @@
       <c r="C11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 2</v>
+      </c>
       <c r="E11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="14"/>
+      <c r="F11" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>William</v>
+      </c>
+      <c r="G11" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Medan</v>
+      </c>
+      <c r="H11" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Padang</v>
+      </c>
+      <c r="I11" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Pasir Kwarsa</v>
+      </c>
+      <c r="J11" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Pupuk</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="6"/>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -1034,66 +1200,99 @@
       <c r="C12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Pelabuhan 2</v>
+      </c>
       <c r="E12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="14"/>
+      <c r="F12" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>William</v>
+      </c>
+      <c r="G12" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Belawan</v>
+      </c>
+      <c r="H12" s="11" t="str">
+        <f t="shared" si="3"/>
+        <v>Pekan Baru</v>
+      </c>
+      <c r="I12" s="11" t="str">
+        <f t="shared" si="4"/>
+        <v>Gyosun</v>
+      </c>
+      <c r="J12" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>Kertas</v>
+      </c>
+      <c r="K12" s="14">
+        <f t="shared" si="6"/>
+        <v>1150000</v>
+      </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="15"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="15">
+        <f>SUM(K3:K12)</f>
+        <v>9925000</v>
+      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="15"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="15">
+        <f>MAX(K3:K12)</f>
+        <v>1250000</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="15"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="15">
+        <f>MIN(K3:K14)</f>
+        <v>675000</v>
+      </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="15"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="15">
+        <f>AVERAGE(K3:K12)</f>
+        <v>992500</v>
+      </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="G18" s="16" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="G18" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C19" s="6" t="s">
@@ -1196,18 +1395,18 @@
       </c>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="F25" s="17" t="s">
+      <c r="D25" s="16"/>
+      <c r="F25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="17"/>
-      <c r="I25" s="17" t="s">
+      <c r="G25" s="16"/>
+      <c r="I25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="J25" s="17"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C26" s="6" t="s">
